--- a/JsonConverter/ExcelFiles/Choice.xlsx
+++ b/JsonConverter/ExcelFiles/Choice.xlsx
@@ -21,46 +21,46 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
   <x:si>
-    <x:t>Arcana_00, Arcana_18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Arcana_14, Arcana_11</x:t>
-  </x:si>
-  <x:si>
     <x:t>ID</x:t>
   </x:si>
   <x:si>
+    <x:t>Dialogue_12,Dialogue_19,Dialogue_27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Stage_01_10,Stage_01_17,Stage_01_24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>선택지 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>카드 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Return ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Choice_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Choice_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ArcanaID</x:t>
+  </x:si>
+  <x:si>
     <x:t>string[]</x:t>
   </x:si>
   <x:si>
-    <x:t>ArcanaID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Choice_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Return ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Choice_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>선택지 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ReurnID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>카드 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Stage_01_10, Stage_01_17, Stage_01_24</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Dialogue_12, Dialogue_19, Dialogue_27</x:t>
+    <x:t>ReturnID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Arcana_14,Arcana_11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Arcana_0,Arcana_18</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -857,10 +857,10 @@
   <x:sheetData>
     <x:row r="1" spans="1:3">
       <x:c r="A1" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B1" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C1" s="5" t="s">
         <x:v>6</x:v>
@@ -868,35 +868,35 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="5" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B2" s="5" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B2" s="5" t="s">
-        <x:v>3</x:v>
-      </x:c>
       <x:c r="C2" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="6" t="s">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B3" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C3" s="6" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3" s="9" customFormat="1">
       <x:c r="A4" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B4" s="10" t="s">
-        <x:v>0</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C4" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
@@ -904,10 +904,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>1</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>12</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
